--- a/userAnalitices/telemetry/Kenya_V1.4.3_User02_-e1-_5534.xlsx
+++ b/userAnalitices/telemetry/Kenya_V1.4.3_User02_-e1-_5534.xlsx
@@ -768,10 +768,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1429,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2027,6 +2027,230 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>⬜ Inactive</t>
         </is>
